--- a/artfynd/A 60766-2021 artfynd.xlsx
+++ b/artfynd/A 60766-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 60766-2021 artfynd.xlsx
+++ b/artfynd/A 60766-2021 artfynd.xlsx
@@ -9258,7 +9258,7 @@
         <v>111109850</v>
       </c>
       <c r="B75" t="n">
-        <v>96265</v>
+        <v>98092</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9299,10 +9299,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>506505.586053042</v>
+        <v>506505</v>
       </c>
       <c r="R75" t="n">
-        <v>6894706.611133874</v>
+        <v>6894707</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9332,19 +9332,9 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2023-07-27</t>
-        </is>
-      </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD75" t="b">

--- a/artfynd/A 60766-2021 artfynd.xlsx
+++ b/artfynd/A 60766-2021 artfynd.xlsx
@@ -9258,7 +9258,7 @@
         <v>111109850</v>
       </c>
       <c r="B75" t="n">
-        <v>98092</v>
+        <v>98102</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>

--- a/artfynd/A 60766-2021 artfynd.xlsx
+++ b/artfynd/A 60766-2021 artfynd.xlsx
@@ -9258,7 +9258,7 @@
         <v>111109850</v>
       </c>
       <c r="B75" t="n">
-        <v>98102</v>
+        <v>98114</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>

--- a/artfynd/A 60766-2021 artfynd.xlsx
+++ b/artfynd/A 60766-2021 artfynd.xlsx
@@ -9258,7 +9258,7 @@
         <v>111109850</v>
       </c>
       <c r="B75" t="n">
-        <v>98114</v>
+        <v>98119</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>

--- a/artfynd/A 60766-2021 artfynd.xlsx
+++ b/artfynd/A 60766-2021 artfynd.xlsx
@@ -9258,7 +9258,7 @@
         <v>111109850</v>
       </c>
       <c r="B75" t="n">
-        <v>98119</v>
+        <v>98128</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9272,11 +9272,6 @@
       </c>
       <c r="E75" t="n">
         <v>219790</v>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>Fläcknycklar</t>
-        </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>

--- a/artfynd/A 60766-2021 artfynd.xlsx
+++ b/artfynd/A 60766-2021 artfynd.xlsx
@@ -9258,7 +9258,7 @@
         <v>111109850</v>
       </c>
       <c r="B75" t="n">
-        <v>98128</v>
+        <v>98141</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9272,6 +9272,11 @@
       </c>
       <c r="E75" t="n">
         <v>219790</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>

--- a/artfynd/A 60766-2021 artfynd.xlsx
+++ b/artfynd/A 60766-2021 artfynd.xlsx
@@ -9258,7 +9258,7 @@
         <v>111109850</v>
       </c>
       <c r="B75" t="n">
-        <v>98141</v>
+        <v>98154</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>

--- a/artfynd/A 60766-2021 artfynd.xlsx
+++ b/artfynd/A 60766-2021 artfynd.xlsx
@@ -9258,7 +9258,7 @@
         <v>111109850</v>
       </c>
       <c r="B75" t="n">
-        <v>98154</v>
+        <v>98157</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>

--- a/artfynd/A 60766-2021 artfynd.xlsx
+++ b/artfynd/A 60766-2021 artfynd.xlsx
@@ -9258,7 +9258,7 @@
         <v>111109850</v>
       </c>
       <c r="B75" t="n">
-        <v>98157</v>
+        <v>98158</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>

--- a/artfynd/A 60766-2021 artfynd.xlsx
+++ b/artfynd/A 60766-2021 artfynd.xlsx
@@ -9258,7 +9258,7 @@
         <v>111109850</v>
       </c>
       <c r="B75" t="n">
-        <v>98158</v>
+        <v>98161</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>

--- a/artfynd/A 60766-2021 artfynd.xlsx
+++ b/artfynd/A 60766-2021 artfynd.xlsx
@@ -9258,7 +9258,7 @@
         <v>111109850</v>
       </c>
       <c r="B75" t="n">
-        <v>98161</v>
+        <v>98264</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>

--- a/artfynd/A 60766-2021 artfynd.xlsx
+++ b/artfynd/A 60766-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY86"/>
+  <dimension ref="A1:AY100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>111108570</v>
+        <v>111109796</v>
       </c>
       <c r="B2" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>1204</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Örasjöberget SÖ, Hls</t>
+          <t>Örasjöberget SO, Ytterhogdal, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>506624.7464981173</v>
+        <v>506393</v>
       </c>
       <c r="R2" t="n">
-        <v>6894517.24150071</v>
+        <v>6894779</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,21 +743,11 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -771,35 +756,41 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
-        </is>
-      </c>
+          <t>Carl Jansson, Roger Adolfsson, Nilla Björklund, Pia Edfors, Helena Björnström, Brian Johnson, Linda Spjut</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>111110335</v>
+        <v>111108524</v>
       </c>
       <c r="B3" t="n">
-        <v>78578</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,37 +798,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Örasjöberget SÖ, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>506636.5840793094</v>
+        <v>506625</v>
       </c>
       <c r="R3" t="n">
-        <v>6894443.476056156</v>
+        <v>6894519</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,40 +855,29 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Linda Spjut</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Linda Spjut</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -911,37 +888,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>111110972</v>
+        <v>111108522</v>
       </c>
       <c r="B4" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -951,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>506615.8914258327</v>
+        <v>506650</v>
       </c>
       <c r="R4" t="n">
-        <v>6894501.345671048</v>
+        <v>6894418</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,19 +956,9 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-07-27</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,12 +973,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1027,50 +989,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>111107033</v>
+        <v>111109814</v>
       </c>
       <c r="B5" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Örasjöberget SÖ, Hls</t>
+          <t>Örasjöberget SO, Ytterhogdal, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>506659.4362012345</v>
+        <v>506568</v>
       </c>
       <c r="R5" t="n">
-        <v>6894476.679518418</v>
+        <v>6894462</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,21 +1057,11 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1123,70 +1070,79 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Nilla Björklund</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Nilla Björklund</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
-        </is>
-      </c>
+          <t>Carl Jansson, Roger Adolfsson, Nilla Björklund, Pia Edfors, Helena Björnström, Brian Johnson, Linda Spjut</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>111110984</v>
+        <v>111111004</v>
       </c>
       <c r="B6" t="n">
-        <v>90666</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Örasjöberget SÖ, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>506452.1984767849</v>
+        <v>506651</v>
       </c>
       <c r="R6" t="n">
-        <v>6894744.801196462</v>
+        <v>6894425</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1216,39 +1172,30 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Linda Spjut</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Linda Spjut</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1259,15 +1206,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>111110958</v>
+        <v>111109795</v>
       </c>
       <c r="B7" t="n">
-        <v>78578</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1275,34 +1217,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Örasjöberget SÖ, Hls</t>
+          <t>Örasjöberget SO, Ytterhogdal, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>506626.1908720845</v>
+        <v>506392</v>
       </c>
       <c r="R7" t="n">
-        <v>6894496.228728455</v>
+        <v>6894827</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1332,19 +1274,9 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-07-27</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1359,31 +1291,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
-        </is>
-      </c>
+          <t>Carl Jansson, Roger Adolfsson, Nilla Björklund, Pia Edfors, Helena Björnström, Brian Johnson, Linda Spjut</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>111108539</v>
+        <v>111110984</v>
       </c>
       <c r="B8" t="n">
-        <v>77268</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1391,21 +1314,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1415,10 +1338,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>506599.586878814</v>
+        <v>506452</v>
       </c>
       <c r="R8" t="n">
-        <v>6894468.15555223</v>
+        <v>6894745</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1448,19 +1371,9 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-07-27</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1475,12 +1388,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1491,15 +1404,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>111108571</v>
+        <v>111109801</v>
       </c>
       <c r="B9" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1507,34 +1415,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Örasjöberget SÖ, Hls</t>
+          <t>Örasjöberget SO, Ytterhogdal, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>506612.1818866885</v>
+        <v>506477</v>
       </c>
       <c r="R9" t="n">
-        <v>6894484.99285731</v>
+        <v>6894623</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1564,21 +1472,11 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1587,57 +1485,63 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
-        </is>
-      </c>
+          <t>Carl Jansson, Roger Adolfsson, Nilla Björklund, Pia Edfors, Helena Björnström, Brian Johnson, Linda Spjut</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>111110464</v>
+        <v>111109906</v>
       </c>
       <c r="B10" t="n">
-        <v>78578</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1646,14 +1550,14 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Örasjöberget SÖ, Hls</t>
+          <t>Örasjöberget SÖ , Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>506653.9048611409</v>
+        <v>506547</v>
       </c>
       <c r="R10" t="n">
-        <v>6894435.570793218</v>
+        <v>6894637</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1683,19 +1587,9 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2023-07-27</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1727,50 +1621,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>111108581</v>
+        <v>111109797</v>
       </c>
       <c r="B11" t="n">
-        <v>103288</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221144</v>
+        <v>6437</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Örasjöberget SÖ, Hls</t>
+          <t>Örasjöberget SO, Ytterhogdal, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>506642.3119931961</v>
+        <v>506416</v>
       </c>
       <c r="R11" t="n">
-        <v>6894622.352138856</v>
+        <v>6894776</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1800,21 +1689,11 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1823,35 +1702,41 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
-        </is>
-      </c>
+          <t>Carl Jansson, Roger Adolfsson, Nilla Björklund, Pia Edfors, Helena Björnström, Brian Johnson, Linda Spjut</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>111106995</v>
+        <v>111107016</v>
       </c>
       <c r="B12" t="n">
-        <v>77268</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1859,21 +1744,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1883,10 +1768,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>506504.3217397507</v>
+        <v>506435</v>
       </c>
       <c r="R12" t="n">
-        <v>6894634.692105664</v>
+        <v>6894774</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1916,19 +1801,9 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2023-07-27</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1959,37 +1834,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>111110952</v>
+        <v>111107017</v>
       </c>
       <c r="B13" t="n">
-        <v>95532</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1999,10 +1869,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>506577.6212545838</v>
+        <v>506448</v>
       </c>
       <c r="R13" t="n">
-        <v>6894459.706294385</v>
+        <v>6894797</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2032,19 +1902,9 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2023-07-27</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2059,12 +1919,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Nilla Björklund</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Nilla Björklund</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -2075,54 +1935,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>111110148</v>
+        <v>111107018</v>
       </c>
       <c r="B14" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Örasjöberget SÖ, Hls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>506604.0645560089</v>
+        <v>506506</v>
       </c>
       <c r="R14" t="n">
-        <v>6894569.972895453</v>
+        <v>6894637</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2152,40 +2003,29 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Linda Spjut</t>
+          <t>Nilla Björklund</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Linda Spjut</t>
+          <t>Nilla Björklund</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2196,50 +2036,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>111109812</v>
+        <v>111107020</v>
       </c>
       <c r="B15" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Örasjöberget SO, Ytterhogdal, Hls</t>
+          <t>Örasjöberget SÖ, Hls</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>506583.5865412534</v>
+        <v>506528</v>
       </c>
       <c r="R15" t="n">
-        <v>6894518.561942493</v>
+        <v>6894651</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2269,19 +2104,9 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2023-07-27</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2296,62 +2121,61 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Nilla Björklund</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Carl Jansson, Roger Adolfsson, Nilla Björklund, Pia Edfors, Helena Björnström, Brian Johnson, Linda Spjut</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
+          <t>Nilla Björklund</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>111109809</v>
+        <v>111107021</v>
       </c>
       <c r="B16" t="n">
-        <v>78612</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6464</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Örasjöberget SO, Ytterhogdal, Hls</t>
+          <t>Örasjöberget SÖ, Hls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>506579.3435743925</v>
+        <v>506663</v>
       </c>
       <c r="R16" t="n">
-        <v>6894535.833058647</v>
+        <v>6894474</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2381,21 +2205,11 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2404,46 +2218,30 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Nilla Björklund</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Carl Jansson, Roger Adolfsson, Nilla Björklund, Pia Edfors, Helena Björnström, Brian Johnson, Linda Spjut</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
+          <t>Nilla Björklund</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>111110365</v>
+        <v>111108558</v>
       </c>
       <c r="B17" t="n">
-        <v>78578</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2451,37 +2249,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Örasjöberget SÖ, Hls</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>506645.953841638</v>
+        <v>506420</v>
       </c>
       <c r="R17" t="n">
-        <v>6894435.555117152</v>
+        <v>6894756</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2511,40 +2306,29 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Linda Spjut</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Linda Spjut</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2555,15 +2339,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>111109810</v>
+        <v>111108559</v>
       </c>
       <c r="B18" t="n">
-        <v>78578</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2571,34 +2350,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Örasjöberget SO, Ytterhogdal, Hls</t>
+          <t>Örasjöberget SÖ, Hls</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>506581.6838626481</v>
+        <v>506441</v>
       </c>
       <c r="R18" t="n">
-        <v>6894534.903605589</v>
+        <v>6894705</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2628,21 +2407,11 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2651,68 +2420,52 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Carl Jansson, Roger Adolfsson, Nilla Björklund, Pia Edfors, Helena Björnström, Brian Johnson, Linda Spjut</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr"/>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>111108569</v>
+        <v>111108560</v>
       </c>
       <c r="B19" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2722,10 +2475,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>506633.5932201581</v>
+        <v>506499</v>
       </c>
       <c r="R19" t="n">
-        <v>6894537.340349417</v>
+        <v>6894608</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2755,19 +2508,9 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2023-07-27</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2798,15 +2541,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>111109813</v>
+        <v>111108561</v>
       </c>
       <c r="B20" t="n">
-        <v>78578</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2814,34 +2552,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Örasjöberget SO, Ytterhogdal, Hls</t>
+          <t>Örasjöberget SÖ, Hls</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>506570.582954744</v>
+        <v>506628</v>
       </c>
       <c r="R20" t="n">
-        <v>6894471.368055934</v>
+        <v>6894469</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2871,21 +2609,11 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2894,46 +2622,30 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Carl Jansson, Roger Adolfsson, Nilla Björklund, Pia Edfors, Helena Björnström, Brian Johnson, Linda Spjut</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr"/>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>111107017</v>
+        <v>111110265</v>
       </c>
       <c r="B21" t="n">
-        <v>77267</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2959,16 +2671,19 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Örasjöberget SÖ, Hls</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>506448.3571598397</v>
+        <v>506577</v>
       </c>
       <c r="R21" t="n">
-        <v>6894797.095269174</v>
+        <v>6894439</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2998,39 +2713,30 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Nilla Björklund</t>
+          <t>Linda Spjut</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Nilla Björklund</t>
+          <t>Linda Spjut</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -3041,50 +2747,48 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>111110973</v>
+        <v>111110286</v>
       </c>
       <c r="B22" t="n">
-        <v>103288</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221144</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Örasjöberget SÖ, Hls</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>506639.730228411</v>
+        <v>506527</v>
       </c>
       <c r="R22" t="n">
-        <v>6894508.397723112</v>
+        <v>6894649</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3114,39 +2818,30 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Linda Spjut</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Linda Spjut</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -3157,37 +2852,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>111110968</v>
+        <v>111108510</v>
       </c>
       <c r="B23" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3197,10 +2887,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>506500.615408694</v>
+        <v>506441</v>
       </c>
       <c r="R23" t="n">
-        <v>6894616.472074421</v>
+        <v>6894705</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3230,19 +2920,9 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2023-07-27</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3257,12 +2937,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -3273,37 +2953,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>111106997</v>
+        <v>111108532</v>
       </c>
       <c r="B24" t="n">
-        <v>77268</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>6456</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3313,10 +2988,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>506687.5075405543</v>
+        <v>506599</v>
       </c>
       <c r="R24" t="n">
-        <v>6894472.064879616</v>
+        <v>6894468</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3346,39 +3021,30 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Nilla Björklund</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Nilla Björklund</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3389,50 +3055,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>111106994</v>
+        <v>111110938</v>
       </c>
       <c r="B25" t="n">
-        <v>77268</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228912</v>
+        <v>6456</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Örasjöberget SÖ, Hls</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>506437.6491871352</v>
+        <v>506591</v>
       </c>
       <c r="R25" t="n">
-        <v>6894771.858156931</v>
+        <v>6894464</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3462,39 +3126,30 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Nilla Björklund</t>
+          <t>Linda Spjut</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Nilla Björklund</t>
+          <t>Linda Spjut</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3505,15 +3160,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>111107018</v>
+        <v>111107009</v>
       </c>
       <c r="B26" t="n">
-        <v>77267</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3521,21 +3171,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3545,10 +3195,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>506506.1888538428</v>
+        <v>506669</v>
       </c>
       <c r="R26" t="n">
-        <v>6894636.563689723</v>
+        <v>6894460</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3578,19 +3228,9 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2023-07-27</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3621,15 +3261,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>111108560</v>
+        <v>111107010</v>
       </c>
       <c r="B27" t="n">
-        <v>77267</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3637,21 +3272,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3661,10 +3296,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>506499.697144461</v>
+        <v>506665</v>
       </c>
       <c r="R27" t="n">
-        <v>6894607.59732495</v>
+        <v>6894454</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3694,19 +3329,9 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2023-07-27</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3721,12 +3346,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Nilla Björklund</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Nilla Björklund</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3737,15 +3362,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>111109808</v>
+        <v>111108545</v>
       </c>
       <c r="B28" t="n">
-        <v>78578</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3771,21 +3391,16 @@
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Örasjöberget SO, Ytterhogdal, Hls</t>
+          <t>Örasjöberget SÖ, Hls</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>506577.4245325426</v>
+        <v>506597</v>
       </c>
       <c r="R28" t="n">
-        <v>6894560.580728585</v>
+        <v>6894470</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3815,21 +3430,11 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3838,46 +3443,30 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Carl Jansson, Roger Adolfsson, Nilla Björklund, Pia Edfors, Helena Björnström, Brian Johnson, Linda Spjut</t>
-        </is>
-      </c>
-      <c r="AY28" t="inlineStr"/>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>111110605</v>
+        <v>111108546</v>
       </c>
       <c r="B29" t="n">
-        <v>78578</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3903,19 +3492,16 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Örasjöberget SÖ , Hls</t>
+          <t>Örasjöberget SÖ, Hls</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>506649.7111504333</v>
+        <v>506658</v>
       </c>
       <c r="R29" t="n">
-        <v>6894427.62311576</v>
+        <v>6894427</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3945,40 +3531,29 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Linda Spjut</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Linda Spjut</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3989,15 +3564,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>111109906</v>
+        <v>111108547</v>
       </c>
       <c r="B30" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4005,37 +3575,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Örasjöberget SÖ , Hls</t>
+          <t>Örasjöberget SÖ, Hls</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>506547.3437118006</v>
+        <v>506650</v>
       </c>
       <c r="R30" t="n">
-        <v>6894637.11032861</v>
+        <v>6894418</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4065,40 +3632,29 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Linda Spjut</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Linda Spjut</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -4109,37 +3665,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>111108518</v>
+        <v>111108548</v>
       </c>
       <c r="B31" t="n">
-        <v>78605</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4149,10 +3700,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>506657.6640323202</v>
+        <v>506627</v>
       </c>
       <c r="R31" t="n">
-        <v>6894426.704755211</v>
+        <v>6894389</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4182,19 +3733,9 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2023-07-27</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4225,15 +3766,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>111107021</v>
+        <v>111109808</v>
       </c>
       <c r="B32" t="n">
-        <v>77267</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4241,34 +3777,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Örasjöberget SÖ, Hls</t>
+          <t>Örasjöberget SO, Ytterhogdal, Hls</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>506663.1833475104</v>
+        <v>506577</v>
       </c>
       <c r="R32" t="n">
-        <v>6894473.88481151</v>
+        <v>6894561</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4298,21 +3839,11 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4321,70 +3852,76 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Nilla Björklund</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Nilla Björklund</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
-        </is>
-      </c>
+          <t>Carl Jansson, Roger Adolfsson, Nilla Björklund, Pia Edfors, Helena Björnström, Brian Johnson, Linda Spjut</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>111107032</v>
+        <v>111109810</v>
       </c>
       <c r="B33" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Örasjöberget SÖ, Hls</t>
+          <t>Örasjöberget SO, Ytterhogdal, Hls</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>506656.1429375879</v>
+        <v>506581</v>
       </c>
       <c r="R33" t="n">
-        <v>6894486.480375513</v>
+        <v>6894534</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4414,21 +3951,11 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4437,70 +3964,76 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Nilla Björklund</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Nilla Björklund</t>
-        </is>
-      </c>
-      <c r="AY33" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
-        </is>
-      </c>
+          <t>Carl Jansson, Roger Adolfsson, Nilla Björklund, Pia Edfors, Helena Björnström, Brian Johnson, Linda Spjut</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>111107035</v>
+        <v>111109813</v>
       </c>
       <c r="B34" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Örasjöberget SÖ, Hls</t>
+          <t>Örasjöberget SO, Ytterhogdal, Hls</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>506661.8282080126</v>
+        <v>506571</v>
       </c>
       <c r="R34" t="n">
-        <v>6894449.597106082</v>
+        <v>6894472</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4530,21 +4063,11 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4553,70 +4076,76 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Nilla Björklund</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Nilla Björklund</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
-        </is>
-      </c>
+          <t>Carl Jansson, Roger Adolfsson, Nilla Björklund, Pia Edfors, Helena Björnström, Brian Johnson, Linda Spjut</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>111108568</v>
+        <v>111109815</v>
       </c>
       <c r="B35" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Örasjöberget SÖ, Hls</t>
+          <t>Örasjöberget SO, Ytterhogdal, Hls</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>506611.4102513329</v>
+        <v>506567</v>
       </c>
       <c r="R35" t="n">
-        <v>6894640.037282292</v>
+        <v>6894461</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4646,21 +4175,11 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4669,76 +4188,79 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
-        </is>
-      </c>
-      <c r="AY35" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
-        </is>
-      </c>
+          <t>Carl Jansson, Roger Adolfsson, Nilla Björklund, Pia Edfors, Helena Björnström, Brian Johnson, Linda Spjut</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>111110938</v>
+        <v>111110107</v>
       </c>
       <c r="B36" t="n">
-        <v>78512</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Örasjöberget SÖ, Hls</t>
+          <t>Örasjöberget SO, Ytterhogdal, Hls</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>506591.6441505086</v>
+        <v>506577</v>
       </c>
       <c r="R36" t="n">
-        <v>6894463.936847929</v>
+        <v>6894472</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4765,40 +4287,29 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Linda Spjut</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Linda Spjut</t>
+          <t>Carl Jansson, Roger Adolfsson, Nilla Björklund, Pia Edfors, Linda Spjut, Brian Johnson, Helena Björnström</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
@@ -4809,15 +4320,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>111108559</v>
+        <v>111110110</v>
       </c>
       <c r="B37" t="n">
-        <v>77267</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4825,34 +4331,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Örasjöberget SÖ, Hls</t>
+          <t>Örasjöberget SO, Ytterhogdal, Hls</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>506441.5180156753</v>
+        <v>506553</v>
       </c>
       <c r="R37" t="n">
-        <v>6894705.087198433</v>
+        <v>6894535</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4882,19 +4388,9 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2023-07-27</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4909,12 +4405,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Carl Jansson, Roger Adolfsson, Nilla Björklund, Pia Edfors, Linda Spjut, Brian Johnson, Helena Björnström</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -4925,15 +4421,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>111110402</v>
+        <v>111110335</v>
       </c>
       <c r="B38" t="n">
-        <v>78578</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4968,10 +4459,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>506642.6660959381</v>
+        <v>506637</v>
       </c>
       <c r="R38" t="n">
-        <v>6894442.553984085</v>
+        <v>6894443</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5001,19 +4492,9 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2023-07-27</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5045,15 +4526,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>111110960</v>
+        <v>111110365</v>
       </c>
       <c r="B39" t="n">
-        <v>78578</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5079,16 +4555,19 @@
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Örasjöberget SÖ, Hls</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>506574.3400463977</v>
+        <v>506646</v>
       </c>
       <c r="R39" t="n">
-        <v>6894463.436055102</v>
+        <v>6894435</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5118,39 +4597,30 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Linda Spjut</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Linda Spjut</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
@@ -5161,15 +4631,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>111108546</v>
+        <v>111110402</v>
       </c>
       <c r="B40" t="n">
-        <v>78578</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5195,16 +4660,19 @@
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Örasjöberget SÖ, Hls</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>506657.6640323202</v>
+        <v>506643</v>
       </c>
       <c r="R40" t="n">
-        <v>6894426.704755211</v>
+        <v>6894442</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5234,39 +4702,30 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Linda Spjut</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Linda Spjut</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -5277,15 +4736,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>111110750</v>
+        <v>111110464</v>
       </c>
       <c r="B41" t="n">
-        <v>78578</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5320,10 +4774,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>506652.0460068331</v>
+        <v>506654</v>
       </c>
       <c r="R41" t="n">
-        <v>6894429.495817178</v>
+        <v>6894436</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5353,19 +4807,9 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2023-07-27</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5397,50 +4841,48 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>111107029</v>
+        <v>111110605</v>
       </c>
       <c r="B42" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Örasjöberget SÖ, Hls</t>
+          <t>Örasjöberget SÖ , Hls</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>506481.2214732352</v>
+        <v>506650</v>
       </c>
       <c r="R42" t="n">
-        <v>6894730.380418526</v>
+        <v>6894428</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5470,39 +4912,30 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Nilla Björklund</t>
+          <t>Linda Spjut</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Nilla Björklund</t>
+          <t>Linda Spjut</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -5513,15 +4946,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>111108538</v>
+        <v>111110750</v>
       </c>
       <c r="B43" t="n">
-        <v>77268</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5529,34 +4957,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Örasjöberget SÖ, Hls</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>506441.5180156753</v>
+        <v>506652</v>
       </c>
       <c r="R43" t="n">
-        <v>6894705.087198433</v>
+        <v>6894430</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5586,39 +5017,30 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Linda Spjut</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Linda Spjut</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -5629,15 +5051,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>111107042</v>
+        <v>111110780</v>
       </c>
       <c r="B44" t="n">
-        <v>76495</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5645,34 +5062,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6487</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Örasjöberget SÖ, Hls</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>506463.5351827472</v>
+        <v>506661</v>
       </c>
       <c r="R44" t="n">
-        <v>6894685.982840234</v>
+        <v>6894431</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5702,39 +5122,30 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Nilla Björklund</t>
+          <t>Linda Spjut</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Nilla Björklund</t>
+          <t>Linda Spjut</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5745,15 +5156,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>111107020</v>
+        <v>111110816</v>
       </c>
       <c r="B45" t="n">
-        <v>77267</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5761,34 +5167,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Örasjöberget SÖ, Hls</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>506528.1417519606</v>
+        <v>506669</v>
       </c>
       <c r="R45" t="n">
-        <v>6894651.082941996</v>
+        <v>6894445</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5818,39 +5227,30 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Nilla Björklund</t>
+          <t>Linda Spjut</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Nilla Björklund</t>
+          <t>Linda Spjut</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5861,54 +5261,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>111110130</v>
+        <v>111110958</v>
       </c>
       <c r="B46" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Örasjöberget SÖ, Hls</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>506657.9897682661</v>
+        <v>506626</v>
       </c>
       <c r="R46" t="n">
-        <v>6894498.626424276</v>
+        <v>6894496</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5938,40 +5329,29 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Linda Spjut</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Linda Spjut</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5982,37 +5362,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>111108572</v>
+        <v>111110960</v>
       </c>
       <c r="B47" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -6022,10 +5397,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>506646.8772911664</v>
+        <v>506575</v>
       </c>
       <c r="R47" t="n">
-        <v>6894441.628235407</v>
+        <v>6894464</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6055,19 +5430,9 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2023-07-27</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6082,12 +5447,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -6098,37 +5463,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>111107031</v>
+        <v>111106988</v>
       </c>
       <c r="B48" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6138,10 +5498,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>506655.1752850328</v>
+        <v>506672</v>
       </c>
       <c r="R48" t="n">
-        <v>6894502.823999159</v>
+        <v>6894457</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6171,19 +5531,9 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2023-07-27</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6214,37 +5564,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>111106986</v>
+        <v>111108518</v>
       </c>
       <c r="B49" t="n">
-        <v>78081</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>229821</v>
+        <v>6462</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6254,10 +5599,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>506685.1708820038</v>
+        <v>506658</v>
       </c>
       <c r="R49" t="n">
-        <v>6894471.126210548</v>
+        <v>6894427</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6287,19 +5632,9 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2023-07-27</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6314,12 +5649,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Nilla Björklund</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Nilla Björklund</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -6330,37 +5665,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>111110780</v>
+        <v>111111025</v>
       </c>
       <c r="B50" t="n">
-        <v>78578</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6369,14 +5699,14 @@
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Örasjöberget SÖ, Hls</t>
+          <t>Örasjöberget SÖ , Hls</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>506660.9296894872</v>
+        <v>506656</v>
       </c>
       <c r="R50" t="n">
-        <v>6894430.914421692</v>
+        <v>6894428</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6406,19 +5736,9 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2023-07-27</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6450,53 +5770,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>111110286</v>
+        <v>111108555</v>
       </c>
       <c r="B51" t="n">
-        <v>77267</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6446</v>
+        <v>6464</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Örasjöberget SÖ, Hls</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>506527.2100128669</v>
+        <v>506597</v>
       </c>
       <c r="R51" t="n">
-        <v>6894649.213163877</v>
+        <v>6894470</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6526,40 +5838,29 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Linda Spjut</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Linda Spjut</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -6570,50 +5871,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>111108545</v>
+        <v>111109809</v>
       </c>
       <c r="B52" t="n">
-        <v>78578</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Örasjöberget SÖ, Hls</t>
+          <t>Örasjöberget SO, Ytterhogdal, Hls</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>506596.3093078738</v>
+        <v>506579</v>
       </c>
       <c r="R52" t="n">
-        <v>6894470.017215576</v>
+        <v>6894535</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6643,21 +5939,11 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
@@ -6666,70 +5952,76 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
-        </is>
-      </c>
-      <c r="AY52" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
-        </is>
-      </c>
+          <t>Carl Jansson, Roger Adolfsson, Nilla Björklund, Pia Edfors, Helena Björnström, Brian Johnson, Linda Spjut</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>111107009</v>
+        <v>111110108</v>
       </c>
       <c r="B53" t="n">
-        <v>78578</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Örasjöberget SÖ, Hls</t>
+          <t>Örasjöberget SO, Ytterhogdal, Hls</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>506668.3557660484</v>
+        <v>506586</v>
       </c>
       <c r="R53" t="n">
-        <v>6894459.884461586</v>
+        <v>6894474</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6759,19 +6051,9 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2023-07-27</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6786,12 +6068,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Nilla Björklund</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Nilla Björklund</t>
+          <t>Carl Jansson, Roger Adolfsson, Nilla Björklund, Pia Edfors, Linda Spjut, Brian Johnson, Helena Björnström</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6802,37 +6084,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>111107030</v>
+        <v>111107042</v>
       </c>
       <c r="B54" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78334</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>6487</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6842,10 +6119,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>506630.2642861524</v>
+        <v>506464</v>
       </c>
       <c r="R54" t="n">
-        <v>6894565.354247081</v>
+        <v>6894686</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6875,19 +6152,9 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2023-07-27</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6918,15 +6185,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>111106996</v>
+        <v>111109794</v>
       </c>
       <c r="B55" t="n">
-        <v>77268</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6934,34 +6196,39 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Örasjöberget SÖ, Hls</t>
+          <t>Örasjöberget SO, Ytterhogdal, Hls</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>506530.9478147675</v>
+        <v>506465</v>
       </c>
       <c r="R55" t="n">
-        <v>6894651.088374661</v>
+        <v>6894836</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6991,19 +6258,9 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2023-07-27</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7018,53 +6275,44 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Nilla Björklund</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Nilla Björklund</t>
-        </is>
-      </c>
-      <c r="AY55" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
-        </is>
-      </c>
+          <t>Carl Jansson, Roger Adolfsson, Nilla Björklund, Pia Edfors, Helena Björnström, Brian Johnson, Linda Spjut</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>111108561</v>
+        <v>111106987</v>
       </c>
       <c r="B56" t="n">
-        <v>77267</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -7074,10 +6322,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>506628.582598392</v>
+        <v>506508</v>
       </c>
       <c r="R56" t="n">
-        <v>6894469.146449759</v>
+        <v>6894664</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7107,19 +6355,9 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2023-07-27</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7134,12 +6372,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Nilla Björklund</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Nilla Björklund</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -7150,50 +6388,49 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>111108573</v>
+        <v>111109850</v>
       </c>
       <c r="B57" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Örasjöberget SÖ, Hls</t>
+          <t>Örasjöberget SÖ , Hls</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>506650.1981954698</v>
+        <v>506505</v>
       </c>
       <c r="R57" t="n">
-        <v>6894417.816547652</v>
+        <v>6894707</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7223,39 +6460,30 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Linda Spjut</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Linda Spjut</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -7266,37 +6494,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>111108510</v>
+        <v>111107029</v>
       </c>
       <c r="B58" t="n">
-        <v>78107</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7306,10 +6529,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>506441.5180156753</v>
+        <v>506481</v>
       </c>
       <c r="R58" t="n">
-        <v>6894705.087198433</v>
+        <v>6894730</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7339,19 +6562,9 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2023-07-27</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7366,12 +6579,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Nilla Björklund</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Nilla Björklund</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -7382,37 +6595,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>111108532</v>
+        <v>111107030</v>
       </c>
       <c r="B59" t="n">
-        <v>78512</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7422,10 +6630,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>506599.586878814</v>
+        <v>506630</v>
       </c>
       <c r="R59" t="n">
-        <v>6894468.15555223</v>
+        <v>6894565</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7455,40 +6663,29 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Nilla Björklund</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Nilla Björklund</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -7499,53 +6696,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>111111004</v>
+        <v>111107031</v>
       </c>
       <c r="B60" t="n">
-        <v>78579</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Örasjöberget SÖ, Hls</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>506651.1198004279</v>
+        <v>506655</v>
       </c>
       <c r="R60" t="n">
-        <v>6894424.823745162</v>
+        <v>6894503</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7575,40 +6764,29 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Linda Spjut</t>
+          <t>Nilla Björklund</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Linda Spjut</t>
+          <t>Nilla Björklund</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
@@ -7619,53 +6797,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>111111025</v>
+        <v>111107032</v>
       </c>
       <c r="B61" t="n">
-        <v>78605</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Örasjöberget SÖ , Hls</t>
+          <t>Örasjöberget SÖ, Hls</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>506655.7913561229</v>
+        <v>506656</v>
       </c>
       <c r="R61" t="n">
-        <v>6894427.63510842</v>
+        <v>6894487</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7695,40 +6865,29 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Linda Spjut</t>
+          <t>Nilla Björklund</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Linda Spjut</t>
+          <t>Nilla Björklund</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
@@ -7739,53 +6898,45 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>111110912</v>
+        <v>111107033</v>
       </c>
       <c r="B62" t="n">
-        <v>77268</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Örasjöberget SÖ, Hls</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>506593.5131369485</v>
+        <v>506659</v>
       </c>
       <c r="R62" t="n">
-        <v>6894464.874539786</v>
+        <v>6894477</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7815,40 +6966,29 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Linda Spjut</t>
+          <t>Nilla Björklund</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Linda Spjut</t>
+          <t>Nilla Björklund</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -7859,37 +6999,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>111107016</v>
+        <v>111107034</v>
       </c>
       <c r="B63" t="n">
-        <v>77267</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7899,10 +7034,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>506434.8396607987</v>
+        <v>506672</v>
       </c>
       <c r="R63" t="n">
-        <v>6894773.72070183</v>
+        <v>6894457</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7932,19 +7067,9 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2023-07-27</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7975,15 +7100,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>111110970</v>
+        <v>111107035</v>
       </c>
       <c r="B64" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8015,10 +7135,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>506550.3202981238</v>
+        <v>506662</v>
       </c>
       <c r="R64" t="n">
-        <v>6894549.319815157</v>
+        <v>6894450</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8048,19 +7168,9 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2023-07-27</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8075,12 +7185,12 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Nilla Björklund</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Nilla Björklund</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
@@ -8091,37 +7201,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>111106988</v>
+        <v>111107036</v>
       </c>
       <c r="B65" t="n">
-        <v>78605</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -8131,10 +7236,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>506672.5706424096</v>
+        <v>506620</v>
       </c>
       <c r="R65" t="n">
-        <v>6894457.090675872</v>
+        <v>6894395</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8164,19 +7269,9 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2023-07-27</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8207,53 +7302,45 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>111110816</v>
+        <v>111108566</v>
       </c>
       <c r="B66" t="n">
-        <v>78578</v>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Örasjöberget SÖ, Hls</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>506668.8530181749</v>
+        <v>506449</v>
       </c>
       <c r="R66" t="n">
-        <v>6894444.940770413</v>
+        <v>6894835</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8283,40 +7370,29 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Linda Spjut</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Linda Spjut</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
@@ -8327,37 +7403,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>111108547</v>
+        <v>111108567</v>
       </c>
       <c r="B67" t="n">
-        <v>78578</v>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8367,10 +7438,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>506650.1981954698</v>
+        <v>506469</v>
       </c>
       <c r="R67" t="n">
-        <v>6894417.816547652</v>
+        <v>6894627</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8400,19 +7471,9 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2023-07-27</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8443,37 +7504,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>111108555</v>
+        <v>111108568</v>
       </c>
       <c r="B68" t="n">
-        <v>78612</v>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8483,10 +7539,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>506596.3093078738</v>
+        <v>506611</v>
       </c>
       <c r="R68" t="n">
-        <v>6894470.017215576</v>
+        <v>6894640</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8516,19 +7572,9 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2023-07-27</t>
-        </is>
-      </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8559,15 +7605,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>111108524</v>
+        <v>111108569</v>
       </c>
       <c r="B69" t="n">
-        <v>89845</v>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8575,21 +7616,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8599,10 +7640,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>506624.7428289601</v>
+        <v>506633</v>
       </c>
       <c r="R69" t="n">
-        <v>6894519.10954137</v>
+        <v>6894538</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8632,19 +7673,9 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2023-07-27</t>
-        </is>
-      </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8675,37 +7706,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>111108537</v>
+        <v>111108570</v>
       </c>
       <c r="B70" t="n">
-        <v>77268</v>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8715,10 +7741,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>506419.9092056306</v>
+        <v>506625</v>
       </c>
       <c r="R70" t="n">
-        <v>6894755.480111708</v>
+        <v>6894517</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8748,19 +7774,9 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2023-07-27</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8791,37 +7807,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>111108522</v>
+        <v>111108571</v>
       </c>
       <c r="B71" t="n">
-        <v>78579</v>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8831,10 +7842,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>506650.1981954698</v>
+        <v>506612</v>
       </c>
       <c r="R71" t="n">
-        <v>6894417.816547652</v>
+        <v>6894485</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8864,19 +7875,9 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2023-07-27</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8907,37 +7908,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>111107010</v>
+        <v>111108572</v>
       </c>
       <c r="B72" t="n">
-        <v>78578</v>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8947,10 +7943,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>506665.5615422573</v>
+        <v>506647</v>
       </c>
       <c r="R72" t="n">
-        <v>6894453.807672432</v>
+        <v>6894441</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8980,19 +7976,9 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2023-07-27</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9007,12 +7993,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Nilla Björklund</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Nilla Björklund</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
@@ -9023,15 +8009,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>111110971</v>
+        <v>111108573</v>
       </c>
       <c r="B73" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9063,10 +8044,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>506638.7810460528</v>
+        <v>506650</v>
       </c>
       <c r="R73" t="n">
-        <v>6894515.40104729</v>
+        <v>6894418</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9096,19 +8077,9 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2023-07-27</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9123,12 +8094,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
@@ -9139,15 +8110,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>111107034</v>
+        <v>111108574</v>
       </c>
       <c r="B74" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9179,10 +8145,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>506672.5706424096</v>
+        <v>506618</v>
       </c>
       <c r="R74" t="n">
-        <v>6894457.090675872</v>
+        <v>6894399</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9212,19 +8178,9 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2023-07-27</t>
-        </is>
-      </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9239,12 +8195,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Nilla Björklund</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Nilla Björklund</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
@@ -9255,54 +8211,45 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>111109850</v>
+        <v>111109798</v>
       </c>
       <c r="B75" t="n">
-        <v>98264</v>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Örasjöberget SÖ , Hls</t>
+          <t>Örasjöberget SO, Ytterhogdal, Hls</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>506505</v>
+        <v>506450</v>
       </c>
       <c r="R75" t="n">
-        <v>6894707</v>
+        <v>6894650</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9343,60 +8290,50 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Linda Spjut</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Linda Spjut</t>
-        </is>
-      </c>
-      <c r="AY75" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
-        </is>
-      </c>
+          <t>Carl Jansson, Roger Adolfsson, Nilla Björklund, Pia Edfors, Helena Björnström, Brian Johnson, Linda Spjut</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>111109797</v>
+        <v>111109812</v>
       </c>
       <c r="B76" t="n">
-        <v>76918</v>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6437</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -9406,10 +8343,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>506415.6620423023</v>
+        <v>506584</v>
       </c>
       <c r="R76" t="n">
-        <v>6894775.552070162</v>
+        <v>6894519</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9439,21 +8376,11 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
@@ -9462,21 +8389,6 @@
       </c>
       <c r="AG76" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ76" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK76" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO76" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
@@ -9493,50 +8405,45 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>111108558</v>
+        <v>111110106</v>
       </c>
       <c r="B77" t="n">
-        <v>77267</v>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Örasjöberget SÖ, Hls</t>
+          <t>Örasjöberget SO, Ytterhogdal, Hls</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>506419.9092056306</v>
+        <v>506587</v>
       </c>
       <c r="R77" t="n">
-        <v>6894755.480111708</v>
+        <v>6894470</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9566,19 +8473,9 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2023-07-27</t>
-        </is>
-      </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9593,12 +8490,12 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Carl Jansson, Roger Adolfsson, Nilla Björklund, Pia Edfors, Linda Spjut, Brian Johnson, Helena Björnström</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
@@ -9612,12 +8509,7 @@
         <v>111110109</v>
       </c>
       <c r="B78" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9653,10 +8545,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>506569.5283863631</v>
+        <v>506570</v>
       </c>
       <c r="R78" t="n">
-        <v>6894532.544858126</v>
+        <v>6894532</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9686,19 +8578,9 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2023-07-27</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9729,50 +8611,49 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>111110107</v>
+        <v>111110112</v>
       </c>
       <c r="B79" t="n">
-        <v>78578</v>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Örasjöberget SO, Ytterhogdal, Hls</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>506577.1298728624</v>
+        <v>506543</v>
       </c>
       <c r="R79" t="n">
-        <v>6894471.847834582</v>
+        <v>6894551</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -9802,19 +8683,9 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2023-07-27</t>
-        </is>
-      </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9845,15 +8716,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>111110106</v>
+        <v>111110113</v>
       </c>
       <c r="B80" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9878,17 +8744,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr"/>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Örasjöberget SO, Ytterhogdal, Hls</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>506587.4229651479</v>
+        <v>506506</v>
       </c>
       <c r="R80" t="n">
-        <v>6894469.999848193</v>
+        <v>6894564</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9918,19 +8788,9 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2023-07-27</t>
-        </is>
-      </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9964,12 +8824,7 @@
         <v>111110114</v>
       </c>
       <c r="B81" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10001,10 +8856,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>506520.7708764967</v>
+        <v>506521</v>
       </c>
       <c r="R81" t="n">
-        <v>6894593.160986268</v>
+        <v>6894593</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10034,19 +8889,9 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2023-07-27</t>
-        </is>
-      </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10077,53 +8922,52 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>111110110</v>
+        <v>111110115</v>
       </c>
       <c r="B82" t="n">
-        <v>78578</v>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Örasjöberget SO, Ytterhogdal, Hls</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>506553.6231749783</v>
+        <v>506522</v>
       </c>
       <c r="R82" t="n">
-        <v>6894534.381954496</v>
+        <v>6894563</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -10150,19 +8994,9 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2023-07-27</t>
-        </is>
-      </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10193,15 +9027,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>111110112</v>
+        <v>111110130</v>
       </c>
       <c r="B83" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10226,24 +9055,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Örasjöberget SO, Ytterhogdal, Hls</t>
+          <t>Örasjöberget SÖ, Hls</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>506542.3659233573</v>
+        <v>506658</v>
       </c>
       <c r="R83" t="n">
-        <v>6894551.172406053</v>
+        <v>6894499</v>
       </c>
       <c r="S83" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -10270,39 +9099,30 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Linda Spjut</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Carl Jansson, Roger Adolfsson, Nilla Björklund, Pia Edfors, Linda Spjut, Brian Johnson, Helena Björnström</t>
+          <t>Linda Spjut</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr">
@@ -10313,50 +9133,49 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>111110108</v>
+        <v>111110148</v>
       </c>
       <c r="B84" t="n">
-        <v>78612</v>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Örasjöberget SO, Ytterhogdal, Hls</t>
+          <t>Örasjöberget SÖ, Hls</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>506586.4802647443</v>
+        <v>506604</v>
       </c>
       <c r="R84" t="n">
-        <v>6894473.734153844</v>
+        <v>6894570</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10386,39 +9205,30 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD84" t="b">
         <v>0</v>
       </c>
       <c r="AE84" t="b">
         <v>0</v>
       </c>
+      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Linda Spjut</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Carl Jansson, Roger Adolfsson, Nilla Björklund, Pia Edfors, Linda Spjut, Brian Johnson, Helena Björnström</t>
+          <t>Linda Spjut</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">
@@ -10429,15 +9239,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>111110115</v>
+        <v>111110968</v>
       </c>
       <c r="B85" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10462,24 +9267,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+      <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Örasjöberget SO, Ytterhogdal, Hls</t>
+          <t>Örasjöberget SÖ, Hls</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>506522.2326332042</v>
+        <v>506500</v>
       </c>
       <c r="R85" t="n">
-        <v>6894562.808575784</v>
+        <v>6894617</v>
       </c>
       <c r="S85" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -10506,19 +9307,9 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2023-07-27</t>
-        </is>
-      </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10533,12 +9324,12 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Carl Jansson, Roger Adolfsson, Nilla Björklund, Pia Edfors, Linda Spjut, Brian Johnson, Helena Björnström</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr">
@@ -10549,15 +9340,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>111110113</v>
+        <v>111110970</v>
       </c>
       <c r="B86" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10582,21 +9368,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Örasjöberget SO, Ytterhogdal, Hls</t>
+          <t>Örasjöberget SÖ, Hls</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>506506.3293926034</v>
+        <v>506551</v>
       </c>
       <c r="R86" t="n">
-        <v>6894563.711870726</v>
+        <v>6894550</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10626,19 +9408,9 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z86" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2023-07-27</t>
-        </is>
-      </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10653,15 +9425,1433 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Carl Jansson, Roger Adolfsson, Nilla Björklund, Pia Edfors, Linda Spjut, Brian Johnson, Helena Björnström</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>111110971</v>
+      </c>
+      <c r="B87" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Örasjöberget SÖ, Hls</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>506639</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6894515</v>
+      </c>
+      <c r="S87" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Brian Johnson</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Brian Johnson</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>111110972</v>
+      </c>
+      <c r="B88" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Örasjöberget SÖ, Hls</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>506616</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6894501</v>
+      </c>
+      <c r="S88" t="n">
+        <v>10</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Brian Johnson</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Brian Johnson</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>111108581</v>
+      </c>
+      <c r="B89" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Örasjöberget SÖ, Hls</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>506643</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6894623</v>
+      </c>
+      <c r="S89" t="n">
+        <v>10</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>111110973</v>
+      </c>
+      <c r="B90" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Örasjöberget SÖ, Hls</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>506640</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6894509</v>
+      </c>
+      <c r="S90" t="n">
+        <v>10</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Brian Johnson</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Brian Johnson</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>111110952</v>
+      </c>
+      <c r="B91" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Örasjöberget SÖ, Hls</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>506577</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6894460</v>
+      </c>
+      <c r="S91" t="n">
+        <v>10</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Brian Johnson</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Brian Johnson</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>111106994</v>
+      </c>
+      <c r="B92" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Örasjöberget SÖ, Hls</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>506438</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6894772</v>
+      </c>
+      <c r="S92" t="n">
+        <v>10</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Nilla Björklund</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Nilla Björklund</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>111106995</v>
+      </c>
+      <c r="B93" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Örasjöberget SÖ, Hls</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>506504</v>
+      </c>
+      <c r="R93" t="n">
+        <v>6894635</v>
+      </c>
+      <c r="S93" t="n">
+        <v>10</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Nilla Björklund</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Nilla Björklund</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>111106996</v>
+      </c>
+      <c r="B94" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Örasjöberget SÖ, Hls</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>506531</v>
+      </c>
+      <c r="R94" t="n">
+        <v>6894651</v>
+      </c>
+      <c r="S94" t="n">
+        <v>10</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Nilla Björklund</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Nilla Björklund</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>111106997</v>
+      </c>
+      <c r="B95" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Örasjöberget SÖ, Hls</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>506687</v>
+      </c>
+      <c r="R95" t="n">
+        <v>6894472</v>
+      </c>
+      <c r="S95" t="n">
+        <v>10</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Nilla Björklund</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Nilla Björklund</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>111108537</v>
+      </c>
+      <c r="B96" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Örasjöberget SÖ, Hls</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>506420</v>
+      </c>
+      <c r="R96" t="n">
+        <v>6894756</v>
+      </c>
+      <c r="S96" t="n">
+        <v>10</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>111108538</v>
+      </c>
+      <c r="B97" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Örasjöberget SÖ, Hls</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>506441</v>
+      </c>
+      <c r="R97" t="n">
+        <v>6894705</v>
+      </c>
+      <c r="S97" t="n">
+        <v>10</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>111108539</v>
+      </c>
+      <c r="B98" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Örasjöberget SÖ, Hls</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>506599</v>
+      </c>
+      <c r="R98" t="n">
+        <v>6894468</v>
+      </c>
+      <c r="S98" t="n">
+        <v>10</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>111110912</v>
+      </c>
+      <c r="B99" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Örasjöberget SÖ, Hls</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>506593</v>
+      </c>
+      <c r="R99" t="n">
+        <v>6894465</v>
+      </c>
+      <c r="S99" t="n">
+        <v>10</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF99" t="inlineStr"/>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Linda Spjut</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Linda Spjut</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>111106986</v>
+      </c>
+      <c r="B100" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Örasjöberget SÖ, Hls</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>506685</v>
+      </c>
+      <c r="R100" t="n">
+        <v>6894471</v>
+      </c>
+      <c r="S100" t="n">
+        <v>10</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Nilla Björklund</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>Nilla Björklund</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>

--- a/artfynd/A 60766-2021 artfynd.xlsx
+++ b/artfynd/A 60766-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY100"/>
+  <dimension ref="A1:AZ100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111109796</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -896,6 +906,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111109814</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111109795</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1094,6 +1114,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111110984</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1206,6 +1231,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111109801</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1311,6 +1341,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111109906</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1423,6 +1458,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111109797</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1524,6 +1564,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111107016</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1625,6 +1670,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111107017</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1726,6 +1776,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111107018</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1827,6 +1882,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111107020</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1928,6 +1988,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111108558</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2029,6 +2094,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111108559</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2128,6 +2198,11 @@
       <c r="AY15" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
+        </is>
+      </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111108560</t>
         </is>
       </c>
     </row>
@@ -2235,6 +2310,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111110265</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2340,6 +2420,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111110286</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2441,6 +2526,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111108510</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2558,6 +2648,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111109808</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2670,6 +2765,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111109810</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2782,6 +2882,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111109813</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2894,6 +2999,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111109815</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2995,6 +3105,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111110107</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3096,6 +3211,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111110110</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3197,6 +3317,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111110960</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3309,6 +3434,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111109809</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3410,6 +3540,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111110108</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3511,6 +3646,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111107042</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3613,6 +3753,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111109794</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3712,6 +3857,11 @@
       <c r="AY30" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
+        </is>
+      </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111106987</t>
         </is>
       </c>
     </row>
@@ -3820,6 +3970,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111109850</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3921,6 +4076,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111107029</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4022,6 +4182,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111108566</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4123,6 +4288,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111108567</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4220,6 +4390,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111109798</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4317,6 +4492,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111109812</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4418,6 +4598,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111110106</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4523,6 +4708,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111110109</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4628,6 +4818,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111110112</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4733,6 +4928,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111110113</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4834,6 +5034,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111110114</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4939,6 +5144,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111110115</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5040,6 +5250,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111110968</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5141,6 +5356,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111110970</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5242,6 +5462,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111110952</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5343,6 +5568,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111106994</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5444,6 +5674,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111106995</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5545,6 +5780,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111106996</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5646,6 +5886,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111108537</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5747,6 +5992,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111108538</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5848,6 +6098,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111108524</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5947,6 +6202,11 @@
       <c r="AY52" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
+        </is>
+      </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111108522</t>
         </is>
       </c>
     </row>
@@ -6054,6 +6314,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111111004</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6155,6 +6420,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111107021</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6256,6 +6526,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111108561</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6356,6 +6631,11 @@
       <c r="AY56" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
+        </is>
+      </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111108532</t>
         </is>
       </c>
     </row>
@@ -6463,6 +6743,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111110938</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6564,6 +6849,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111107009</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6665,6 +6955,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111107010</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6766,6 +7061,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111108545</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6867,6 +7167,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111108546</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6968,6 +7273,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111108547</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7067,6 +7377,11 @@
       <c r="AY63" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
+        </is>
+      </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111108548</t>
         </is>
       </c>
     </row>
@@ -7174,6 +7489,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111110335</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7279,6 +7599,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111110365</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7384,6 +7709,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111110402</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7489,6 +7819,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111110464</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7594,6 +7929,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111110605</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7699,6 +8039,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111110750</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7804,6 +8149,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111110780</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7909,6 +8259,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111110816</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8010,6 +8365,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111110958</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8111,6 +8471,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111106988</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8210,6 +8575,11 @@
       <c r="AY74" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
+        </is>
+      </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111108518</t>
         </is>
       </c>
     </row>
@@ -8317,6 +8687,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111111025</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8418,6 +8793,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111108555</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8519,6 +8899,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111107030</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8620,6 +9005,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111107031</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8721,6 +9111,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111107032</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8822,6 +9217,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111107033</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8923,6 +9323,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111107034</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9024,6 +9429,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111107035</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9125,6 +9535,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111107036</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9226,6 +9641,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111108568</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9327,6 +9747,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111108569</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9428,6 +9853,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111108570</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9529,6 +9959,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111108571</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9630,6 +10065,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111108572</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9731,6 +10171,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111108573</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9830,6 +10275,11 @@
       <c r="AY90" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
+        </is>
+      </c>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111108574</t>
         </is>
       </c>
     </row>
@@ -9938,6 +10388,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111110130</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10044,6 +10499,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111110148</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10145,6 +10605,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111110971</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10246,6 +10711,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111110972</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10347,6 +10817,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111108581</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10448,6 +10923,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111110973</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10549,6 +11029,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111106997</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10648,6 +11133,11 @@
       <c r="AY98" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
+        </is>
+      </c>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111108539</t>
         </is>
       </c>
     </row>
@@ -10755,6 +11245,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111110912</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10856,8 +11351,114 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111106986</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>